--- a/data/trans_dic/IP16_n_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16_n_R2-Provincia-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,57; 66,81</t>
+          <t>23,24; 68,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,35; 58,08</t>
+          <t>18,87; 60,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 21,17</t>
+          <t>1,85; 21,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,68; 65,43</t>
+          <t>18,39; 70,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,51</t>
+          <t>3,49; 34,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 32,19</t>
+          <t>4,03; 33,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 33,23</t>
+          <t>2,02; 31,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,91; 60,62</t>
+          <t>27,5; 59,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,46; 38,18</t>
+          <t>13,42; 39,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 17,8</t>
+          <t>2,19; 18,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 18,68</t>
+          <t>4,34; 20,53</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,67; 60,25</t>
+          <t>22,09; 59,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 27,86</t>
+          <t>3,99; 29,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 24,14</t>
+          <t>3,66; 25,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,35; 44,85</t>
+          <t>7,06; 45,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,77; 62,19</t>
+          <t>26,87; 61,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 20,42</t>
+          <t>2,34; 19,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,22; 49,29</t>
+          <t>18,76; 50,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,07; 47,08</t>
+          <t>23,78; 45,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,1; 55,36</t>
+          <t>30,01; 55,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 17,56</t>
+          <t>3,96; 17,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 31,07</t>
+          <t>11,71; 31,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,74; 39,92</t>
+          <t>12,32; 40,64</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,7; 68,4</t>
+          <t>19,32; 69,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,55; 44,82</t>
+          <t>9,06; 45,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,41</t>
+          <t>0,0; 44,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,85; 45,89</t>
+          <t>14,25; 47,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 52,84</t>
+          <t>5,98; 47,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,29; 38,22</t>
+          <t>9,43; 39,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,33; 45,51</t>
+          <t>11,27; 45,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,07; 51,7</t>
+          <t>18,92; 52,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,76; 34,65</t>
+          <t>11,23; 34,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,3</t>
+          <t>0,0; 23,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,68; 39,55</t>
+          <t>16,79; 40,69</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,59; 54,92</t>
+          <t>18,19; 56,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 30,66</t>
+          <t>3,39; 30,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,58; 38,34</t>
+          <t>11,31; 38,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,91; 61,02</t>
+          <t>13,8; 60,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,41; 79,26</t>
+          <t>40,55; 79,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 41,21</t>
+          <t>4,16; 36,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 20,39</t>
+          <t>2,46; 21,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,08; 74,0</t>
+          <t>18,12; 73,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,28; 63,08</t>
+          <t>34,32; 61,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 29,18</t>
+          <t>6,51; 26,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,07; 23,97</t>
+          <t>8,46; 24,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,9; 59,12</t>
+          <t>21,9; 59,37</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,99; 71,56</t>
+          <t>17,81; 72,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 49,56</t>
+          <t>6,14; 48,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,04</t>
+          <t>0,0; 52,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,75; 76,66</t>
+          <t>26,97; 75,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,25; 59,97</t>
+          <t>9,3; 67,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 38,55</t>
+          <t>0,0; 38,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,2</t>
+          <t>0,0; 51,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 51,13</t>
+          <t>8,88; 50,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,04; 57,51</t>
+          <t>18,3; 58,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,93; 35,97</t>
+          <t>8,75; 36,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 38,33</t>
+          <t>4,71; 39,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,77; 55,84</t>
+          <t>21,02; 56,58</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,89; 73,56</t>
+          <t>26,89; 72,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,39; 47,2</t>
+          <t>4,45; 49,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,88</t>
+          <t>0,0; 37,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,52; 82,49</t>
+          <t>40,91; 88,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,03</t>
+          <t>0,0; 20,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,48</t>
+          <t>0,0; 52,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,88; 67,24</t>
+          <t>24,77; 66,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39,87; 70,96</t>
+          <t>38,87; 72,07</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,59; 22,05</t>
+          <t>2,61; 22,96</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,71</t>
+          <t>0,0; 31,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,67; 48,71</t>
+          <t>17,63; 48,2</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,02; 42,43</t>
+          <t>12,79; 43,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,14; 30,68</t>
+          <t>6,68; 32,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,46; 47,96</t>
+          <t>8,8; 46,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,28; 67,25</t>
+          <t>36,35; 66,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,68; 56,44</t>
+          <t>25,45; 55,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 19,93</t>
+          <t>2,57; 19,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,12</t>
+          <t>0,0; 36,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22,42; 53,03</t>
+          <t>23,08; 51,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,85; 45,13</t>
+          <t>22,98; 45,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,54; 21,91</t>
+          <t>6,27; 21,71</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,07; 32,89</t>
+          <t>9,14; 35,15</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,31; 54,65</t>
+          <t>31,12; 54,15</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,72; 53,11</t>
+          <t>22,73; 51,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,66; 24,11</t>
+          <t>2,69; 23,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,43; 21,38</t>
+          <t>2,47; 21,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,38; 81,79</t>
+          <t>24,79; 80,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,71; 39,92</t>
+          <t>17,75; 40,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,13; 44,84</t>
+          <t>11,26; 43,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,32; 19,11</t>
+          <t>2,35; 21,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,06; 84,08</t>
+          <t>35,25; 84,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,64; 41,36</t>
+          <t>22,54; 40,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,34; 29,09</t>
+          <t>8,54; 29,4</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 15,83</t>
+          <t>3,57; 16,13</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>38,06; 74,67</t>
+          <t>37,53; 74,44</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31,2; 45,46</t>
+          <t>31,69; 45,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,31; 24,09</t>
+          <t>12,8; 23,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,86; 17,99</t>
+          <t>8,15; 17,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16,74; 36,68</t>
+          <t>17,21; 36,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,21; 45,73</t>
+          <t>33,45; 46,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,47; 18,56</t>
+          <t>9,66; 19,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,48; 19,58</t>
+          <t>9,32; 19,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27,42; 40,25</t>
+          <t>27,46; 39,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>34,62; 44,5</t>
+          <t>34,24; 43,93</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12,07; 19,5</t>
+          <t>12,31; 19,62</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,06; 17,16</t>
+          <t>10,05; 16,86</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24,05; 35,86</t>
+          <t>23,89; 36,22</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2750; 7796</t>
+          <t>2712; 8001</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2792; 9347</t>
+          <t>3036; 9660</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2224,47 +2224,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>620; 6433</t>
+          <t>562; 6613</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2267; 7940</t>
+          <t>2232; 8520</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5685</t>
+          <t>649; 6437</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>790; 6183</t>
+          <t>775; 6343</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>441; 7417</t>
+          <t>451; 6927</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6405; 14430</t>
+          <t>6545; 14162</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4673; 13259</t>
+          <t>4659; 13592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>770; 6285</t>
+          <t>772; 6363</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1921; 9848</t>
+          <t>2288; 10822</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3792; 10079</t>
+          <t>3695; 9973</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>677; 6543</t>
+          <t>937; 6986</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>636; 6581</t>
+          <t>998; 6910</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4001; 28280</t>
+          <t>4450; 28917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5315; 12349</t>
+          <t>5336; 12271</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>583; 5101</t>
+          <t>583; 4816</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3768; 10195</t>
+          <t>3881; 10468</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11113; 22673</t>
+          <t>11451; 22023</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11012; 20255</t>
+          <t>10978; 20203</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2170; 8508</t>
+          <t>1919; 8689</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5499; 14898</t>
+          <t>5612; 15324</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13054; 44397</t>
+          <t>13706; 45203</t>
         </is>
       </c>
     </row>
@@ -2625,32 +2625,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2290; 7953</t>
+          <t>2246; 8106</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1329; 6961</t>
+          <t>1407; 7104</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4229</t>
+          <t>0; 4208</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2485; 8232</t>
+          <t>2556; 8559</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>640; 5580</t>
+          <t>631; 4997</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2072; 8528</t>
+          <t>2104; 8848</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,27 +2660,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2095; 9232</t>
+          <t>2285; 9305</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4676; 11472</t>
+          <t>4197; 11727</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4828; 13111</t>
+          <t>4248; 12878</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4162</t>
+          <t>0; 4243</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5994; 15117</t>
+          <t>6418; 15553</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2712; 8981</t>
+          <t>2975; 9242</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>858; 5923</t>
+          <t>655; 5905</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2756; 9125</t>
+          <t>2691; 9268</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1742; 7640</t>
+          <t>1728; 7605</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6474; 13019</t>
+          <t>6661; 13078</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>676; 6281</t>
+          <t>634; 5539</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>619; 5215</t>
+          <t>630; 5419</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1226; 8194</t>
+          <t>2006; 8163</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10909; 20676</t>
+          <t>11249; 20253</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2222; 10085</t>
+          <t>2250; 9112</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3983; 11836</t>
+          <t>4179; 12198</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5167; 13949</t>
+          <t>5168; 14008</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1459; 6531</t>
+          <t>1625; 6581</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>891; 7190</t>
+          <t>891; 7083</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3388</t>
+          <t>0; 3394</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2121; 6314</t>
+          <t>2222; 6202</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>723; 4690</t>
+          <t>727; 5270</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>635; 4737</t>
+          <t>0; 4730</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2904</t>
+          <t>0; 2656</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>825; 5465</t>
+          <t>949; 5442</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3227; 9746</t>
+          <t>3102; 9913</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2394; 9637</t>
+          <t>2344; 9653</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>558; 4476</t>
+          <t>550; 4666</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3742; 10568</t>
+          <t>3979; 10709</t>
         </is>
       </c>
     </row>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3452; 9106</t>
+          <t>3329; 9000</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>483; 5186</t>
+          <t>489; 5442</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3264,47 +3264,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2986</t>
+          <t>0; 2888</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4347; 8850</t>
+          <t>4389; 9444</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3805</t>
+          <t>0; 3725</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5165</t>
+          <t>0; 4588</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3249; 9150</t>
+          <t>3370; 9067</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9213; 16398</t>
+          <t>8982; 16654</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>753; 6413</t>
+          <t>760; 6678</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5641</t>
+          <t>0; 5559</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3762; 10370</t>
+          <t>3753; 10260</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2799; 9122</t>
+          <t>2750; 9392</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1632; 8149</t>
+          <t>1775; 8579</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1348; 6834</t>
+          <t>1254; 6683</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10805; 20031</t>
+          <t>10827; 19835</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6811; 14970</t>
+          <t>6751; 14754</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>638; 5050</t>
+          <t>652; 5026</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3300</t>
+          <t>0; 3877</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9946; 23522</t>
+          <t>10237; 22948</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10495; 21674</t>
+          <t>11034; 21741</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3396; 11372</t>
+          <t>3254; 11269</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2006; 8174</t>
+          <t>2271; 8737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23956; 40519</t>
+          <t>23073; 40150</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5631; 13768</t>
+          <t>5893; 13471</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>564; 5117</t>
+          <t>570; 4995</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>508; 4473</t>
+          <t>517; 4406</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2059; 6636</t>
+          <t>2011; 6560</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7059; 15913</t>
+          <t>7075; 16141</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2414; 9726</t>
+          <t>2442; 9355</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>580; 4781</t>
+          <t>588; 5441</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4104; 9844</t>
+          <t>4127; 9875</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14897; 27213</t>
+          <t>14831; 26478</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3580; 12485</t>
+          <t>3665; 12616</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1246; 7271</t>
+          <t>1640; 7410</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7543; 14798</t>
+          <t>7438; 14754</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>39093; 56965</t>
+          <t>39714; 57125</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>19656; 35575</t>
+          <t>18904; 35340</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11295; 22928</t>
+          <t>10393; 22664</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29750; 65193</t>
+          <t>30581; 64467</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>47798; 65808</t>
+          <t>48140; 66271</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15011; 29427</t>
+          <t>15323; 30154</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11687; 24135</t>
+          <t>11485; 24391</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>49952; 73332</t>
+          <t>50027; 72760</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>93218; 119813</t>
+          <t>92190; 118258</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>36973; 59728</t>
+          <t>37709; 60077</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25228; 43032</t>
+          <t>25200; 42264</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>86563; 129050</t>
+          <t>85984; 130359</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16_n_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16_n_R2-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos (tasa de respuesta: 99,76%)</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41,61%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13,17%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14,17%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10,83%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>44,36%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>35,98%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>41,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,17%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,24; 68,57</t>
+          <t>19,4; 65,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,87; 60,03</t>
+          <t>3,6; 31,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>3,85; 32,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1,84; 30,21</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,0; 66,27</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,43; 59,21</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,85; 21,77</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>18,39; 70,21</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,49; 34,55</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,03; 33,03</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 31,03</t>
+          <t>3,52; 25,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,5; 59,5</t>
+          <t>26,75; 58,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,42; 39,14</t>
+          <t>12,63; 37,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 18,03</t>
+          <t>2,23; 18,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 20,53</t>
+          <t>5,3; 22,52</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>44,21%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32,32%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>33,32%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>40,9%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>12,15%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>10,34%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>23,12%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>44,21%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>32,32%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>34,67%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,09; 59,61</t>
+          <t>26,24; 61,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 29,75</t>
+          <t>2,35; 19,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 25,35</t>
+          <t>18,11; 51,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 45,86</t>
+          <t>23,0; 45,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,87; 61,8</t>
+          <t>22,66; 59,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 19,28</t>
+          <t>3,94; 28,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,76; 50,61</t>
+          <t>2,4; 23,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,78; 45,73</t>
+          <t>22,7; 51,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,01; 55,22</t>
+          <t>30,02; 55,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 17,93</t>
+          <t>4,56; 19,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,71; 31,96</t>
+          <t>12,03; 30,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,32; 40,64</t>
+          <t>26,45; 43,97</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23,73%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21,68%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22,54%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>43,95%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>22,83%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>14,54%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>23,73%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,32; 69,72</t>
+          <t>6,41; 50,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,06; 45,75</t>
+          <t>9,91; 37,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,25; 47,7</t>
+          <t>10,01; 39,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 47,32</t>
+          <t>19,78; 68,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,43; 39,66</t>
+          <t>8,88; 45,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 44,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,27; 45,87</t>
+          <t>13,88; 47,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,92; 52,85</t>
+          <t>19,0; 51,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,23; 34,03</t>
+          <t>12,35; 35,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,76</t>
+          <t>0,0; 24,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,79; 40,69</t>
+          <t>14,57; 37,19</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>61,31%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16,41%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,73%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45,25%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>34,8%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,62%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>23,21%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32,9%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>61,31%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,73%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,19; 56,52</t>
+          <t>40,0; 80,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 30,56</t>
+          <t>4,24; 37,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,31; 38,94</t>
+          <t>2,43; 19,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,8; 60,74</t>
+          <t>17,08; 76,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,55; 79,62</t>
+          <t>17,11; 57,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 36,34</t>
+          <t>4,62; 31,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 21,19</t>
+          <t>11,33; 40,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,12; 73,72</t>
+          <t>15,55; 60,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34,32; 61,79</t>
+          <t>34,76; 64,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 26,36</t>
+          <t>6,66; 27,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 24,7</t>
+          <t>8,08; 24,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,9; 59,37</t>
+          <t>21,6; 59,05</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>30,43%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16,39%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11,81%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30,87%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>42,23%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>22,5%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>18,34%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50,86%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>30,43%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16,39%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>41,33%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,81; 72,11</t>
+          <t>9,29; 62,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 48,83</t>
+          <t>0,0; 39,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,13</t>
+          <t>0,0; 62,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,97; 75,29</t>
+          <t>10,63; 56,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 67,39</t>
+          <t>17,8; 72,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,5</t>
+          <t>5,27; 49,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,39</t>
+          <t>0,0; 53,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,88; 50,91</t>
+          <t>27,13; 76,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,3; 58,49</t>
+          <t>18,4; 57,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,75; 36,03</t>
+          <t>8,56; 34,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 39,95</t>
+          <t>4,7; 38,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,02; 56,58</t>
+          <t>23,63; 60,33</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>64,46%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20,35%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>43,65%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>50,07%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>18,76%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>64,46%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,35%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,89; 72,7</t>
+          <t>40,59; 87,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,45; 49,53</t>
+          <t>0,0; 17,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 57,73</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24,06; 63,9</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>27,44; 72,85</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4,33; 49,41</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 37,61</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>40,91; 88,02</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 20,59</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 52,83</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,77; 66,64</t>
+          <t>0,0; 30,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,87; 72,07</t>
+          <t>39,69; 73,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,61; 22,96</t>
+          <t>2,58; 22,47</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,25</t>
+          <t>0,0; 28,85</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,63; 48,2</t>
+          <t>15,28; 45,46</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>39,47%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11,72%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>37,63%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>25,97%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>16,35%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>23,89%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>51,93%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>39,47%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,79; 43,69</t>
+          <t>24,01; 55,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,68; 32,3</t>
+          <t>2,46; 20,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,8; 46,9</t>
+          <t>0,0; 37,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,35; 66,59</t>
+          <t>23,04; 53,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,45; 55,62</t>
+          <t>12,87; 42,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 19,83</t>
+          <t>7,45; 29,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,56</t>
+          <t>8,71; 44,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,08; 51,74</t>
+          <t>35,34; 65,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,98; 45,27</t>
+          <t>22,2; 45,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,27; 21,71</t>
+          <t>6,47; 21,81</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,14; 35,15</t>
+          <t>8,16; 32,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,12; 54,15</t>
+          <t>31,61; 53,7</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>27,82%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>24,94%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>60,96%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>36,58%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>9,34%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>7,96%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>51,86%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>27,82%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>24,94%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,73; 51,96</t>
+          <t>16,3; 39,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,69; 23,54</t>
+          <t>11,14; 45,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,47; 21,06</t>
+          <t>2,34; 21,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,79; 80,86</t>
+          <t>35,54; 83,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,75; 40,49</t>
+          <t>23,59; 51,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,26; 43,13</t>
+          <t>2,68; 24,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,35; 21,75</t>
+          <t>2,44; 22,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,25; 84,36</t>
+          <t>24,01; 79,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,54; 40,25</t>
+          <t>22,64; 40,68</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,54; 29,4</t>
+          <t>8,43; 27,08</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,57; 16,13</t>
+          <t>3,61; 16,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>37,53; 74,44</t>
+          <t>38,26; 75,97</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>39,79%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>33,92%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>38,26%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>17,92%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>12,54%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>28,51%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>39,79%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,78%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31,69; 45,59</t>
+          <t>33,39; 46,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,8; 23,93</t>
+          <t>9,62; 18,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,15; 17,78</t>
+          <t>9,34; 19,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,21; 36,28</t>
+          <t>27,97; 40,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,45; 46,05</t>
+          <t>31,22; 45,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,66; 19,02</t>
+          <t>13,13; 23,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,32; 19,79</t>
+          <t>8,02; 17,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27,46; 39,93</t>
+          <t>28,14; 40,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>34,24; 43,93</t>
+          <t>34,4; 44,24</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12,31; 19,62</t>
+          <t>12,48; 19,8</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,05; 16,86</t>
+          <t>9,91; 17,11</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,89; 36,22</t>
+          <t>30,27; 39,25</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos (tasa de respuesta: 99,76%)</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,62 +2141,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5050</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2722</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>5176</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>5790</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2525</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5050</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>10225</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8245</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>2722</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2422</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10225</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8245</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2722</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4443</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2712; 8001</t>
+          <t>2354; 8005</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3036; 9660</t>
+          <t>671; 5869</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>740; 6146</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>356; 5822</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2684; 7732</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2966; 9528</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>562; 6613</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2232; 8520</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>649; 6437</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>775; 6343</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>451; 6927</t>
+          <t>732; 5341</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6545; 14162</t>
+          <t>6368; 13965</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4659; 13592</t>
+          <t>4385; 13085</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>772; 6363</t>
+          <t>788; 6614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2288; 10822</t>
+          <t>2123; 9024</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8779</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6685</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14216</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6842</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2852</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2818</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14576</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8779</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1821</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6685</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>14018</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30900</t>
+          <t>28235</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3695; 9973</t>
+          <t>5211; 12233</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>937; 6986</t>
+          <t>587; 4750</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>998; 6910</t>
+          <t>3745; 10658</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4450; 28917</t>
+          <t>9814; 19444</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5336; 12271</t>
+          <t>3790; 9983</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>583; 4816</t>
+          <t>926; 6732</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3881; 10468</t>
+          <t>655; 6368</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11451; 22023</t>
+          <t>8800; 19946</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10978; 20203</t>
+          <t>10985; 20306</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1919; 8689</t>
+          <t>2209; 9521</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5612; 15324</t>
+          <t>5767; 14650</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13706; 45203</t>
+          <t>21541; 35808</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2506</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3985</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5110</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3545</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1385</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5011</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2506</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4835</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>8632</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2246; 8106</t>
+          <t>677; 5330</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1407; 7104</t>
+          <t>2211; 8333</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4208</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2556; 8559</t>
+          <t>1770; 7019</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>631; 4997</t>
+          <t>2300; 7995</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2104; 8848</t>
+          <t>1379; 7022</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4233</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2285; 9305</t>
+          <t>2387; 8155</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4197; 11727</t>
+          <t>4216; 11461</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4248; 12878</t>
+          <t>4675; 13341</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4243</t>
+          <t>0; 4464</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6418; 15553</t>
+          <t>5082; 12972</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10071</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4713</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5690</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2632</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>5523</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4119</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10071</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2501</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>8907</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2975; 9242</t>
+          <t>6571; 13152</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>655; 5905</t>
+          <t>646; 5769</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2691; 9268</t>
+          <t>623; 4893</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1728; 7605</t>
+          <t>1779; 7952</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6661; 13078</t>
+          <t>2798; 9456</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>634; 5539</t>
+          <t>893; 6003</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>630; 5419</t>
+          <t>2696; 9549</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2006; 8163</t>
+          <t>1901; 7371</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11249; 20253</t>
+          <t>11392; 21089</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2250; 9112</t>
+          <t>2302; 9372</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4179; 12198</t>
+          <t>3988; 12317</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5168; 14008</t>
+          <t>4890; 13369</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>3854</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3264</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>1194</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4189</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>7514</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1625; 6581</t>
+          <t>727; 4862</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>891; 7083</t>
+          <t>0; 4814</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3394</t>
+          <t>0; 3217</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2222; 6202</t>
+          <t>1036; 5538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>727; 5270</t>
+          <t>1624; 6586</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4730</t>
+          <t>764; 7164</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2656</t>
+          <t>0; 3497</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>949; 5442</t>
+          <t>2290; 6470</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3102; 9913</t>
+          <t>3117; 9807</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2344; 9653</t>
+          <t>2294; 9363</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>550; 4666</t>
+          <t>549; 4500</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3979; 10709</t>
+          <t>4296; 10968</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,62 +3181,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6916</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4993</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>6198</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2062</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6916</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2818</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>1767</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>6115</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>13114</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>2818</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1767</t>
-        </is>
-      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>5564</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3329; 9000</t>
+          <t>4355; 9422</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>489; 5442</t>
+          <t>0; 3170</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>0; 5014</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2751; 7309</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>3396; 9018</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>476; 5429</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0; 2888</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>4389; 9444</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3725</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0; 4588</t>
-        </is>
-      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3370; 9067</t>
+          <t>0; 2352</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8982; 16654</t>
+          <t>9171; 17083</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760; 6678</t>
+          <t>750; 6535</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5559</t>
+          <t>0; 5133</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3753; 10260</t>
+          <t>2918; 8682</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>10471</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>15818</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>5583</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>4342</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>3405</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>15467</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>10471</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2054</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>15420</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>31688</t>
+          <t>31237</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2750; 9392</t>
+          <t>6370; 14770</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1775; 8579</t>
+          <t>624; 5274</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1254; 6683</t>
+          <t>0; 3945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10827; 19835</t>
+          <t>9684; 22446</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6751; 14754</t>
+          <t>2766; 9202</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>652; 5026</t>
+          <t>1978; 7896</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3877</t>
+          <t>1241; 6400</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>10237; 22948</t>
+          <t>10695; 19865</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11034; 21741</t>
+          <t>10664; 21645</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3254; 11269</t>
+          <t>3361; 11322</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2271; 8737</t>
+          <t>2028; 8170</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23073; 40150</t>
+          <t>22854; 38822</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>11091</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>5409</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>7137</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>9483</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>1983</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>1665</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4208</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>11091</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>5409</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>11052</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5893; 13471</t>
+          <t>6498; 15932</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>570; 4995</t>
+          <t>2417; 9823</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>517; 4406</t>
+          <t>586; 5354</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2011; 6560</t>
+          <t>4161; 9790</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7075; 16141</t>
+          <t>6116; 13448</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2442; 9355</t>
+          <t>569; 5244</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>588; 5441</t>
+          <t>511; 4631</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4127; 9875</t>
+          <t>1833; 6096</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14831; 26478</t>
+          <t>14895; 26761</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3665; 12616</t>
+          <t>3617; 11620</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1640; 7410</t>
+          <t>1660; 7725</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7438; 14754</t>
+          <t>7400; 14694</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>57263</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>21844</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>16998</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>55955</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>47937</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>26470</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>15989</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>50663</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>57263</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>21844</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>16998</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>61204</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>111868</t>
+          <t>105583</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>39714; 57125</t>
+          <t>48060; 66398</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>18904; 35340</t>
+          <t>15257; 30041</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10393; 22664</t>
+          <t>11520; 23909</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30581; 64467</t>
+          <t>46133; 66628</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>48140; 66271</t>
+          <t>39115; 57055</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15323; 30154</t>
+          <t>19392; 34820</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11485; 24391</t>
+          <t>10223; 22667</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>50027; 72760</t>
+          <t>40244; 58311</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>92190; 118258</t>
+          <t>92603; 119116</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37709; 60077</t>
+          <t>38212; 60635</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25200; 42264</t>
+          <t>24849; 42911</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>85984; 130359</t>
+          <t>93209; 120878</t>
         </is>
       </c>
     </row>
